--- a/basedatos_partidas/salida/descompuestos/CT-10-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-10-02-040.xlsx
@@ -539,10 +539,10 @@
         <v>5.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="H10" t="n">
-        <v>7.54</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11">
@@ -591,10 +591,10 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="H12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11.69</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="15">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>17.92</v>
+        <v>16.89</v>
       </c>
       <c r="H24" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>18.1</v>
+        <v>17.06</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-10-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-10-02-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 10 Impermeabilizaciones y aislamientos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Impermeabilizantes líquidos y acrílicos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
